--- a/zawodnicy_cz.xlsx
+++ b/zawodnicy_cz.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C119"/>
+  <dimension ref="A1:C117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1558,153 +1558,153 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Stepan</t>
+          <t>Jurij</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Marcanik</t>
+          <t>Medvedev</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>[Słowacja] MSK Puchov</t>
+          <t>[Słowacja] Slovan Bratislava</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Jurij</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Medvedev</t>
+          <t>Naderi</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>[Słowacja] Slovan Bratislava</t>
+          <t>[Szkocja] Glasgow Rangers</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Naderi</t>
+          <t>Naimann</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>[Szkocja] Glasgow Rangers</t>
+          <t>[Słowacja] Slovan Bratislava B</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Pavel</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Naimann</t>
+          <t>Osmancik</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>[Słowacja] Slovan Bratislava B</t>
+          <t>[Nowa Zelandia] Auckland City FC</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Vojtech</t>
+          <t>Tomas</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Novak</t>
+          <t>Ostrák</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>[Słowacja] MFK Ruzomberok B</t>
+          <t>[Stany Zjednaczone] St. Louis CITY SC</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Pavel</t>
+          <t>Dan</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Osmancik</t>
+          <t>Ozvolda</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>[Nowa Zelandia] Auckland City FC</t>
+          <t>[Słowacja] KFC Komarno</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Tomas</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ostrák</t>
+          <t>Palan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>[Stany Zjednaczone] St. Louis CITY SC</t>
+          <t>[Słowacja] KFC Komarno</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Dan</t>
+          <t>Jiri</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ozvolda</t>
+          <t>Pavlenka</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>[Słowacja] KFC Komarno</t>
+          <t>[Grecja] PAOK Thessaloniki</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Jakub</t>
+          <t>Dominik</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Palan</t>
+          <t>Pech</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>[Słowacja] KFC Komarno</t>
+          <t>[Szwajcaria] BSC Young Boys</t>
         </is>
       </c>
     </row>
@@ -1716,471 +1716,471 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Pavlenka</t>
+          <t>Piroch</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>[Grecja] PAOK Thessaloniki</t>
+          <t>[Polska] Odra Opole</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Dominik</t>
+          <t>Radim</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Pech</t>
+          <t>Poboril</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>[Szwajcaria] BSC Young Boys</t>
+          <t>[Słowacja] FC Tatran Presov</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Jiri</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Piroch</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>[Polska] Odra Opole</t>
+          <t>[Słowacja] FK Pohronie</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Radim</t>
+          <t>Roman</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Poboril</t>
+          <t>Potocny</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>[Słowacja] FC Tatran Presov</t>
+          <t>[Słowacja] MFK Skalica</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Jakub</t>
+          <t>Petr</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Pudhorocky</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>[Słowacja] FK Pohronie</t>
+          <t>[Słowacja] MFK Skalica</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Roman</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Potocny</t>
+          <t>Pudil</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>[Słowacja] MFK Skalica</t>
+          <t>[Słowacja] FC ViOn Zlate Moravce-Vrable</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Petr</t>
+          <t>Milos</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Pudhorocky</t>
+          <t>Pudil</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>[Słowacja] MFK Skalica</t>
+          <t>[Łotwa] FS Jelgava</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Tomas</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Pudil</t>
+          <t>Rataj</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>[Słowacja] FC ViOn Zlate Moravce-Vrable</t>
+          <t>[Łotwa] FS Jelgava</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Milos</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Pudil</t>
+          <t>Rehak</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>[Łotwa] FS Jelgava</t>
+          <t>[Słowacja] Slovan Bratislava B</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Tomas</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Rataj</t>
+          <t>Richter</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>[Łotwa] FS Jelgava</t>
+          <t>[Cypr] Krasava Ypsonas FC</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Jakub</t>
+          <t>Pedro</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Rehak</t>
+          <t>Rodriguez Cuesta</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>[Słowacja] Slovan Bratislava B</t>
+          <t>[Słowacja] FK Pohronie</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Ondrej</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Richter</t>
+          <t>Rudzan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>[Cypr] Krasava Ypsonas FC</t>
+          <t>[Indonezja] PSIM Yogyakarta</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Pedro</t>
+          <t>Michal</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Rodriguez Cuesta</t>
+          <t>Sacek</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>[Słowacja] FK Pohronie</t>
+          <t>[Polska] Górnik Zabrze</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Ondrej</t>
+          <t>Lukas</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Rudzan</t>
+          <t>Sadilek</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>[Indonezja] PSIM Yogyakarta</t>
+          <t>[Polska] Górnik Zabrze</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Michal</t>
+          <t>Patrik</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Sacek</t>
+          <t>Schick</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>[Polska] Górnik Zabrze</t>
+          <t>[Niemcy] Bayer 04 Leverkusen</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Lukas</t>
+          <t>Michal</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Sadilek</t>
+          <t>Sevcik</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>[Polska] Górnik Zabrze</t>
+          <t>[Polska] Legia Warszawa</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Patrik</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Schick</t>
+          <t>Severa</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>[Niemcy] Bayer 04 Leverkusen</t>
+          <t>[Słowacja] MFK Bytca</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Michal</t>
+          <t>Radek</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Sevcik</t>
+          <t>Siler</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>[Polska] Legia Warszawa</t>
+          <t>[Portugalia] Rió Ave FC</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Matyas</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Severa</t>
+          <t>Silhavy</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>[Słowacja] MFK Bytca</t>
+          <t>[Słowacja] Dynamo Malzenice</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Radek</t>
+          <t>Stefan</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Siler</t>
+          <t>Simic</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>[Portugalia] Rió Ave FC</t>
+          <t>[Cypr] Omonia Nicosia</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Matyas</t>
+          <t>Matej</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Silhavy</t>
+          <t>Sin</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>[Słowacja] Dynamo Malzenice</t>
+          <t>[Holandia] ADO Den Haag</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Stefan</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Simic</t>
+          <t>Sot</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>[Cypr] Omonia Nicosia</t>
+          <t>[Słowacja] Tatran Liptovsky Mikulas</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Matej</t>
+          <t>Filip</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Sin</t>
+          <t>Soucek</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>[Holandia] ADO Den Haag</t>
+          <t>[Słowacja] MFK Ruzomberok</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Tomáš</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Sot</t>
+          <t>Souček</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>[Słowacja] Tatran Liptovsky Mikulas</t>
+          <t>[Anglia] West Ham United</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Filip</t>
+          <t>Jindrich</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Soucek</t>
+          <t>Stanek</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>[Słowacja] MFK Ruzomberok</t>
+          <t>[Arabia Saudyjska] Al Hazem</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Tomáš</t>
+          <t>Patrizio</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Souček</t>
+          <t>Stronati</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>[Anglia] West Ham United</t>
+          <t>[Węgry] Újpest FC</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Jindrich</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Stanek</t>
+          <t>Suchy</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>[Arabia Saudyjska] Al Hazem</t>
+          <t>[Słowacja] FC Tatran Presov</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Patrizio</t>
+          <t>Pavel</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Stronati</t>
+          <t>Sulc</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>[Węgry] Újpest FC</t>
+          <t>[Francja] Olympique Lyon</t>
         </is>
       </c>
     </row>
@@ -2192,63 +2192,63 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Suchy</t>
+          <t>Svancara</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>[Słowacja] FC Tatran Presov</t>
+          <t>[Słowacja] FC Petrzalka</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Pavel</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Sulc</t>
+          <t>Svitek</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>[Francja] Olympique Lyon</t>
+          <t>[Niemcy] TSV Havelse</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Svancara</t>
+          <t>Tecl</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>[Słowacja] FC Petrzalka</t>
+          <t>[Słowacja] FC Tatran Presov</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Miroslav</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Svitek</t>
+          <t>Tomek</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>[Niemcy] TSV Havelse</t>
+          <t>[Słowacja] Slovan Galanta</t>
         </is>
       </c>
     </row>
@@ -2260,180 +2260,146 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Tecl</t>
+          <t>Trefil</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>[Słowacja] FC Tatran Presov</t>
+          <t>[Słowacja] MFK Dukla Banska Bystrica</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Miroslav</t>
+          <t>Matyas</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Tomek</t>
+          <t>Tresl</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>[Słowacja] Slovan Galanta</t>
+          <t>[Słowacja] FC ViOn Zlate Moravce-Vrable</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Jakub</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Trefil</t>
+          <t>Villaseca</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>[Słowacja] MFK Dukla Banska Bystrica</t>
+          <t>[Meksyk] CD Tapatío</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Matyas</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Tresl</t>
+          <t>Vitík</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>[Słowacja] FC ViOn Zlate Moravce-Vrable</t>
+          <t>[Włochy] FC Bologna</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Radek</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Villaseca</t>
+          <t>Vítek</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>[Meksyk] CD Tapatío</t>
+          <t>[Anglia] FC Middlesbrough</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Dominik</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Vitík</t>
+          <t>Zak</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>[Włochy] FC Bologna</t>
+          <t>[Słowacja] KFC Komarno</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Radek</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Vítek</t>
+          <t>Zamburek</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>[Anglia] FC Middlesbrough</t>
+          <t>[Holandia] ADO Den Haag</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Dominik</t>
+          <t>Lukas</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Zak</t>
+          <t>Zima</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>[Słowacja] KFC Komarno</t>
+          <t>[Rumunia] Petrolul Ploiesti</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Ondrej</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Zamburek</t>
+          <t>Zmrzly</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
-        <is>
-          <t>[Holandia] ADO Den Haag</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Lukas</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Zima</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>[Rumunia] Petrolul Ploiesti</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Ondrej</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Zmrzly</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
         <is>
           <t>[Polska] Górnik Zabrze</t>
         </is>
